--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R66e677a761ac41eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7032108fc27149f0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7032108fc27149f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R954c3ac93e00417f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R954c3ac93e00417f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b7814562f8d42c2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b7814562f8d42c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9274a91109b442ff"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9274a91109b442ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90ebea65f9b34743"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R90ebea65f9b34743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a018e2f38e34b6b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a018e2f38e34b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdee3b6fb34104725"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdee3b6fb34104725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re8d082c510814f80"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re8d082c510814f80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ad325963bdf4ddd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ad325963bdf4ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R652bc1e337fc4fe0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R652bc1e337fc4fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re35859aa769c46a6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re35859aa769c46a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R82a845dd44324b37"/>
   </x:sheets>
 </x:workbook>
 </file>
